--- a/data/file_generation/reference/data_201/商家A产品退货率分析结果_res.xlsx
+++ b/data/file_generation/reference/data_201/商家A产品退货率分析结果_res.xlsx
@@ -3708,18 +3708,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9B3C43A-8753-417F-9ADC-15B545BAB626}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15C7CF5D-270F-4B5B-815D-2906D7A13BB3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94671B4A-C1FD-4AA3-AA3A-B3C49D2ACE50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{767E687C-4167-4E73-9957-EC43770B5015}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D2711B1-B62A-4080-B360-E1CDFDAD04C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0DE7D89-7324-4CDF-8884-EECFB5BDB91A}"/>
 </file>